--- a/04_Network/06_Preserve/c_data/06_preserve.xlsx
+++ b/04_Network/06_Preserve/c_data/06_preserve.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12577" uniqueCount="2105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12613" uniqueCount="2128">
   <si>
     <t>sheet</t>
   </si>
@@ -5944,6 +5944,15 @@
     <t>0.1-6</t>
   </si>
   <si>
+    <t>BiocGenerics</t>
+  </si>
+  <si>
+    <t>0.58.0</t>
+  </si>
+  <si>
+    <t>Bioconductor 3.23 (R 4.6.0)</t>
+  </si>
+  <si>
     <t>BiocManager</t>
   </si>
   <si>
@@ -5956,12 +5965,24 @@
     <t>2.3.4</t>
   </si>
   <si>
+    <t>circlize</t>
+  </si>
+  <si>
+    <t>0.4.18</t>
+  </si>
+  <si>
     <t>cli</t>
   </si>
   <si>
     <t>3.6.6</t>
   </si>
   <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>0.3-68</t>
+  </si>
+  <si>
     <t>cluster</t>
   </si>
   <si>
@@ -5980,6 +6001,18 @@
     <t>2.1-2</t>
   </si>
   <si>
+    <t>ComplexHeatmap</t>
+  </si>
+  <si>
+    <t>2.28.0</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>1.5.3</t>
+  </si>
+  <si>
     <t>data.table</t>
   </si>
   <si>
@@ -6058,6 +6091,12 @@
     <t>0.1.4</t>
   </si>
   <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
     <t>ggplot2</t>
   </si>
   <si>
@@ -6070,6 +6109,9 @@
     <t>0.9.8</t>
   </si>
   <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
     <t>glue</t>
   </si>
   <si>
@@ -6124,7 +6166,10 @@
     <t>1.86.0</t>
   </si>
   <si>
-    <t>Bioconductor 3.23 (R 4.6.0)</t>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
   </si>
   <si>
     <t>iterators</t>
@@ -6196,6 +6241,12 @@
     <t>2.0.3</t>
   </si>
   <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>0.1-9</t>
+  </si>
+  <si>
     <t>preprocessCore</t>
   </si>
   <si>
@@ -6232,6 +6283,12 @@
     <t>1.2.3</t>
   </si>
   <si>
+    <t>rjson</t>
+  </si>
+  <si>
+    <t>0.2.23</t>
+  </si>
+  <si>
     <t>rlang</t>
   </si>
   <si>
@@ -6262,6 +6319,12 @@
     <t>0.18.0</t>
   </si>
   <si>
+    <t>S4Vectors</t>
+  </si>
+  <si>
+    <t>0.50.0</t>
+  </si>
+  <si>
     <t>S7</t>
   </si>
   <si>
@@ -6278,6 +6341,12 @@
   </si>
   <si>
     <t>1.2.4</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>1.4.6.1</t>
   </si>
   <si>
     <t>stringi</t>
@@ -60155,7 +60224,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -60199,15 +60268,15 @@
         <v>1975</v>
       </c>
       <c r="C4" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B5" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="C5" t="s">
         <v>1971</v>
@@ -60215,10 +60284,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B6" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="C6" t="s">
         <v>1971</v>
@@ -60226,10 +60295,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B7" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C7" t="s">
         <v>1971</v>
@@ -60237,10 +60306,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B8" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C8" t="s">
         <v>1971</v>
@@ -60248,10 +60317,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B9" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C9" t="s">
         <v>1971</v>
@@ -60259,10 +60328,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B10" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C10" t="s">
         <v>1971</v>
@@ -60270,10 +60339,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B11" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C11" t="s">
         <v>1971</v>
@@ -60281,10 +60350,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B12" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C12" t="s">
         <v>1971</v>
@@ -60292,21 +60361,21 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B13" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C13" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B14" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="C14" t="s">
         <v>1971</v>
@@ -60314,10 +60383,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B15" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C15" t="s">
         <v>1971</v>
@@ -60325,10 +60394,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B16" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C16" t="s">
         <v>1971</v>
@@ -60336,10 +60405,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B17" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C17" t="s">
         <v>1971</v>
@@ -60347,10 +60416,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B18" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C18" t="s">
         <v>1971</v>
@@ -60358,10 +60427,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B19" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C19" t="s">
         <v>1971</v>
@@ -60369,10 +60438,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B20" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C20" t="s">
         <v>1971</v>
@@ -60380,10 +60449,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B21" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C21" t="s">
         <v>1971</v>
@@ -60391,10 +60460,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B22" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C22" t="s">
         <v>1971</v>
@@ -60402,10 +60471,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B23" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C23" t="s">
         <v>1971</v>
@@ -60413,10 +60482,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B24" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C24" t="s">
         <v>1971</v>
@@ -60424,10 +60493,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B25" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C25" t="s">
         <v>1971</v>
@@ -60435,10 +60504,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B26" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C26" t="s">
         <v>1971</v>
@@ -60446,10 +60515,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C27" t="s">
         <v>1971</v>
@@ -60457,10 +60526,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B28" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C28" t="s">
         <v>1971</v>
@@ -60468,10 +60537,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B29" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C29" t="s">
         <v>1971</v>
@@ -60479,10 +60548,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B30" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C30" t="s">
         <v>1971</v>
@@ -60490,10 +60559,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B31" t="s">
-        <v>2029</v>
+        <v>2022</v>
       </c>
       <c r="C31" t="s">
         <v>1971</v>
@@ -60518,15 +60587,15 @@
         <v>2033</v>
       </c>
       <c r="C33" t="s">
-        <v>2034</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B34" t="s">
         <v>2035</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2036</v>
       </c>
       <c r="C34" t="s">
         <v>1971</v>
@@ -60534,10 +60603,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B35" t="s">
         <v>2037</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2038</v>
       </c>
       <c r="C35" t="s">
         <v>1971</v>
@@ -60545,10 +60614,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B36" t="s">
         <v>2039</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2040</v>
       </c>
       <c r="C36" t="s">
         <v>1971</v>
@@ -60556,10 +60625,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B37" t="s">
         <v>2041</v>
-      </c>
-      <c r="B37" t="s">
-        <v>2042</v>
       </c>
       <c r="C37" t="s">
         <v>1971</v>
@@ -60567,10 +60636,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B38" t="s">
         <v>2043</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1997</v>
       </c>
       <c r="C38" t="s">
         <v>1971</v>
@@ -60595,7 +60664,7 @@
         <v>2047</v>
       </c>
       <c r="C40" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -60606,7 +60675,7 @@
         <v>2049</v>
       </c>
       <c r="C41" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -60658,18 +60727,18 @@
         <v>2058</v>
       </c>
       <c r="B46" t="s">
-        <v>2059</v>
+        <v>2008</v>
       </c>
       <c r="C46" t="s">
-        <v>2034</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B47" t="s">
         <v>2060</v>
-      </c>
-      <c r="B47" t="s">
-        <v>2061</v>
       </c>
       <c r="C47" t="s">
         <v>1971</v>
@@ -60677,10 +60746,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B48" t="s">
         <v>2062</v>
-      </c>
-      <c r="B48" t="s">
-        <v>2063</v>
       </c>
       <c r="C48" t="s">
         <v>1971</v>
@@ -60688,10 +60757,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B49" t="s">
         <v>2064</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2065</v>
       </c>
       <c r="C49" t="s">
         <v>1971</v>
@@ -60699,10 +60768,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B50" t="s">
         <v>2066</v>
-      </c>
-      <c r="B50" t="s">
-        <v>2067</v>
       </c>
       <c r="C50" t="s">
         <v>1971</v>
@@ -60710,10 +60779,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B51" t="s">
         <v>2068</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2069</v>
       </c>
       <c r="C51" t="s">
         <v>1971</v>
@@ -60721,21 +60790,21 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B52" t="s">
         <v>2070</v>
       </c>
-      <c r="B52" t="s">
-        <v>2001</v>
-      </c>
       <c r="C52" t="s">
-        <v>2071</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B53" t="s">
         <v>2072</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2073</v>
       </c>
       <c r="C53" t="s">
         <v>1971</v>
@@ -60743,10 +60812,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B54" t="s">
         <v>2074</v>
-      </c>
-      <c r="B54" t="s">
-        <v>2075</v>
       </c>
       <c r="C54" t="s">
         <v>1971</v>
@@ -60754,21 +60823,21 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B55" t="s">
         <v>2076</v>
       </c>
-      <c r="B55" t="s">
-        <v>2077</v>
-      </c>
       <c r="C55" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B56" t="s">
         <v>2078</v>
-      </c>
-      <c r="B56" t="s">
-        <v>2079</v>
       </c>
       <c r="C56" t="s">
         <v>1971</v>
@@ -60776,10 +60845,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B57" t="s">
         <v>2080</v>
-      </c>
-      <c r="B57" t="s">
-        <v>2081</v>
       </c>
       <c r="C57" t="s">
         <v>1971</v>
@@ -60787,10 +60856,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B58" t="s">
         <v>2082</v>
-      </c>
-      <c r="B58" t="s">
-        <v>2083</v>
       </c>
       <c r="C58" t="s">
         <v>1971</v>
@@ -60798,10 +60867,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B59" t="s">
         <v>2084</v>
-      </c>
-      <c r="B59" t="s">
-        <v>2085</v>
       </c>
       <c r="C59" t="s">
         <v>1971</v>
@@ -60809,10 +60878,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B60" t="s">
         <v>2086</v>
-      </c>
-      <c r="B60" t="s">
-        <v>2087</v>
       </c>
       <c r="C60" t="s">
         <v>1971</v>
@@ -60820,10 +60889,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B61" t="s">
         <v>2088</v>
-      </c>
-      <c r="B61" t="s">
-        <v>2089</v>
       </c>
       <c r="C61" t="s">
         <v>1971</v>
@@ -60831,21 +60900,21 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C62" t="s">
         <v>2090</v>
-      </c>
-      <c r="B62" t="s">
-        <v>2091</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B63" t="s">
         <v>2092</v>
-      </c>
-      <c r="B63" t="s">
-        <v>2093</v>
       </c>
       <c r="C63" t="s">
         <v>1971</v>
@@ -60853,10 +60922,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B64" t="s">
         <v>2094</v>
-      </c>
-      <c r="B64" t="s">
-        <v>2095</v>
       </c>
       <c r="C64" t="s">
         <v>1971</v>
@@ -60864,10 +60933,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B65" t="s">
         <v>2096</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1993</v>
       </c>
       <c r="C65" t="s">
         <v>1971</v>
@@ -60892,7 +60961,7 @@
         <v>2100</v>
       </c>
       <c r="C67" t="s">
-        <v>1971</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -60914,6 +60983,138 @@
         <v>2104</v>
       </c>
       <c r="C69" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C81" t="s">
         <v>1971</v>
       </c>
     </row>
